--- a/www/download/COUNTRY.SVN.zdW16.xlsx
+++ b/www/download/COUNTRY.SVN.zdW16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>Eslovênia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.924345209199789</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.0120845758338</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.00041711471411</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>0.862848456160259</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.801621542630063</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.803041790328925</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.796461112154936</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.730799220109408</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.680381981164095</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.717238749655838</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.754031018580498</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>0.71841341312344</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.778690302578927</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.75295337648931</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.75412598149258</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.906</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.916</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.937</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.932</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.934</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.929</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.944</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1.001</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.983</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.962</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.938</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.927</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.753</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.768</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.772</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.769</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.783</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.833</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.789</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.773</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.763</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.741</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.745</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1460.319</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1452.745</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1520.947</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1524.644</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1554.983</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1512.181</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>1515.366</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>1554.456</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>1608.306</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>1594.986</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>1578.754</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>1537.495</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1494.105</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1495.012</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>1528.746</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1189.232</t>
+          <t>1820122840.80356</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1192.581</t>
+          <t>1818034117.86821</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1248.047</t>
+          <t>1829655283.88765</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1256.695</t>
+          <t>1882856719.01915</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1284.726</t>
+          <t>2035677526.26455</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1251.254</t>
+          <t>1989646943.23468</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1255.526</t>
+          <t>2029475161.2875</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1291.599</t>
+          <t>2065231031.10271</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1337.518</t>
+          <t>2088436377.00394</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1313.15</t>
+          <t>1881664818.9053</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1290.35</t>
+          <t>1886537125.12623</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1252.858</t>
+          <t>1943180651.84343</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1214.124</t>
+          <t>1800784027.89444</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1194.287</t>
+          <t>1732317774.5086</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1212.155</t>
+          <t>1767700261.19881</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>645211397.370462</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>659687500.9277</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>666598399.959995</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>744745115.07258</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>875298211.002777</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>893432957.885647</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>909370594.534995</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>918899213.411196</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>945368714.140154</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>935807439.886879</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>855811561.345628</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>885123962.495499</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>839994679.694612</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>824650585.178988</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>837208249.870978</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2349332.93009213</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2332408.27814959</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2160480.66297575</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1813006.28494678</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1643717.71647332</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1512320.70296175</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1398519.59000482</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1155999.21832884</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1033482.75357552</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1129577.07342247</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1131918.71695041</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1078176.02506245</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1129000.58005833</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1055884.50344351</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1024832.51230726</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8408.13997004549</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8137.6373325351</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>8342.28922575737</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>8972.6890428112</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10004.9321306429</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10545.5166961682</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>11008.2195053734</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>12547.7531018776</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>14132.8224753671</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>12431.5588620166</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>13488.2498779423</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>13895.8401743648</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>13133.7632186359</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>13057.277904618</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>13436.8200929977</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>16510.9527470598</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>16250.517386459</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16474.6916606157</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>18457.534516532</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>21991.508634676</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>23215.5690883793</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>25023.2453513366</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>28564.829417067</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>31504.6311836836</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>25941.3162789218</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>28734.8705366604</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>31557.6808159339</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>28567.0802213017</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>27321.6086143509</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>27976.9797011042</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.843166448774272</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.807796870977405</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.872262219763655</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.687416237537225</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.467758055312561</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.400501278754205</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.380653836340519</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.405593759521509</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.414810940952832</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.403226715272464</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.507750138326163</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.415460492638477</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.445394868978702</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.448233981111871</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.447853625650255</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.924345209199789</t>
+          <t>871.589281438478</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.0120845758338</t>
+          <t>875.985952259653</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00041711471411</t>
+          <t>866.668920184612</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.862848456160259</t>
+          <t>969.947533370555</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.801621542630063</t>
+          <t>1134.1732568873</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803041790328925</t>
+          <t>1161.25265852015</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796461112154936</t>
+          <t>1161.97160084205</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.730799220109408</t>
+          <t>1133.44995548494</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.680381981164095</t>
+          <t>1135.10081544114</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717238749655838</t>
+          <t>1154.40570399546</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.754031018580498</t>
+          <t>1085.11888388907</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.71841341312344</t>
+          <t>1145.50979370187</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778690302578927</t>
+          <t>1101.31461046598</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.75295337648931</t>
+          <t>1113.50488823639</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.75412598149258</t>
+          <t>1123.96559113802</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-68355440.3609583</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2267681.08777853</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>63971232.9761204</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>170732822.745134</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>346462911.152758</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>419264810.107897</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>505172129.891304</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>569429757.824044</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>569101067.431851</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>575602027.890608</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>495515210.898531</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>609455810.718205</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>579716769.423206</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>599842838.930121</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>679248013.182229</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>30165404.0285963</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>95282616.6236571</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>152135641.73497</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>271928729.737509</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>447035840.874567</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>505103659.827528</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>579348508.828199</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>625371073.164736</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>585277577.224026</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>595667351.89177</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>537254788.089651</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>654126731.196591</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>623123534.223117</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>637628839.807048</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>693234187.235982</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-98520844.3895546</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-93014935.5358786</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-88164408.75885</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>-101195906.992375</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-100572929.721809</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>-85838849.7196314</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>-74176378.936895</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-55941315.3406926</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>-16176509.792175</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>-20065324.0011615</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>-41739577.1911199</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>-44670920.4783864</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>-43406764.7999104</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>-37786000.8769275</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>-13986174.0537535</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1606.48412065868</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>1583.60466351516</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1622.63147630501</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1636.70521736865</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1664.69193391642</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>1626.33583321419</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>1604.28054842131</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1593.17018415956</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>1605.95305277061</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1619.89292410935</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>1636.08814728407</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1621.42385691545</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>1591.8344870988</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1612.61561727812</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>1627.33765623532</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1612.59640521474</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1585.51630059093</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1622.46429086277</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1636.37525778333</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1664.82840650558</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>1628.22506710509</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>1604.78490368486</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1593.05561525662</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>1606.98842580037</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>1622.70137931036</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1640.99683193059</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1625.27624459927</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>1593.54236645028</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>1612.75955688745</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1626.06610239379</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>7106.40822497436</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>7709.55157133623</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>9214.29497963264</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>11983.8386947397</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>15632.500773195</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>18034.7229157159</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>21391.80586104</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>27787.1927932275</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>31573.1246592305</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>23968.910515829</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>25661.1753876817</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>29884.709866256</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>27406.6326652176</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>28855.3444935004</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>30812.4829304824</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>432091950.032851</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>453535786.441509</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>487319274.190254</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>524177880.348452</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>621795967.311574</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>662247371.410615</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>716575126.170655</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>748501034.198793</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>762335775.416609</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>636544999.447614</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>681657906.28517</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>761009860.778735</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>724660785.049469</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>711771240.495275</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>733256303.167144</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>9892.17479718426</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>9982.56085658959</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>10976.2557059372</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>13834.6815523874</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>17663.1760190105</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>19741.7793501087</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>22800.7905085769</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>29358.8202510961</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>33157.9845533605</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>24085.252131537</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>26054.7639128103</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>30056.1385554205</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>26763.1391776648</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>27614.4704081975</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>28616.8357702688</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1460.319</t>
+          <t>744703710.176346</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1452.745</t>
+          <t>779322867.505645</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1520.947</t>
+          <t>803653565.109708</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1524.644</t>
+          <t>944792565.690987</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1554.983</t>
+          <t>1218080340.89438</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1512.181</t>
+          <t>1271984118.67479</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1515.366</t>
+          <t>1364426452.8591</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1554.456</t>
+          <t>1454397464.61175</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1608.306</t>
+          <t>1451583170.6079</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1594.986</t>
+          <t>1222053714.97236</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1578.754</t>
+          <t>1207049439.66876</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1537.495</t>
+          <t>1382784669.88665</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1494.105</t>
+          <t>1257827562.73199</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1495.012</t>
+          <t>1220954880.97429</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1528.746</t>
+          <t>1253629331.20835</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1189.232</t>
+          <t>-2785.7665722099</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1192.581</t>
+          <t>-2273.00928525336</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1248.047</t>
+          <t>-1761.96072630459</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1256.695</t>
+          <t>-1850.84285764769</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1284.726</t>
+          <t>-2030.67524581546</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1251.254</t>
+          <t>-1707.05643439274</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1255.526</t>
+          <t>-1408.98464753686</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>1291.599</t>
+          <t>-1571.62745786859</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1337.518</t>
+          <t>-1584.85989412994</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1313.15</t>
+          <t>-116.34161570801</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1290.35</t>
+          <t>-393.588525128602</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1252.858</t>
+          <t>-171.428689164528</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1214.124</t>
+          <t>643.493487552801</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1194.287</t>
+          <t>1240.87408530286</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1212.155</t>
+          <t>2195.64716021364</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2065.576</t>
+          <t>-312611760.143495</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2063.32</t>
+          <t>-325787081.064137</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2067.554</t>
+          <t>-316334290.919454</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2127.72</t>
+          <t>-420614685.342535</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2322.279</t>
+          <t>-596284373.58281</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2274.758</t>
+          <t>-609736747.264171</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2324.454</t>
+          <t>-647851326.688449</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2357.134</t>
+          <t>-705896430.412956</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2397.226</t>
+          <t>-689247395.191292</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2171.944</t>
+          <t>-585508715.524741</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2163.341</t>
+          <t>-525391533.383587</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2249.367</t>
+          <t>-621774809.107912</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2087.254</t>
+          <t>-533166777.682517</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2020.276</t>
+          <t>-509183640.479015</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1767.7</t>
+          <t>-520373028.041209</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9218.77680889371</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>9473.70352630502</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>10642.6783829604</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>13235.986124053</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>15456.0876703891</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>16128.6273166379</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>17510.6762298623</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>21283.8768741006</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>24078.1207701672</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>20881.7986751589</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>19607.5421168365</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>21234.96</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>19428.9297641772</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>20096.94201</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>21215.0068549442</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>926.891</t>
+          <t>0.082716263133222</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>910.402</t>
+          <t>0.0873175552560127</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>926.483</t>
+          <t>0.093415085704269</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>915.306</t>
+          <t>0.0971120371757415</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>926.122</t>
+          <t>0.095687772467665</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>903.784</t>
+          <t>0.0945203180613441</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>892.806</t>
+          <t>0.0989692259283834</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>907.2</t>
+          <t>0.103524143359455</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>936.862</t>
+          <t>0.100184534252094</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>901.729</t>
+          <t>0.0864111146610192</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>885.547</t>
+          <t>0.0815697375675464</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>855.644</t>
+          <t>0.0832713476369236</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>827.913</t>
+          <t>0.0792853148982075</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>827.892</t>
+          <t>0.0790138842547306</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>848.993</t>
+          <t>0.0855368523343503</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10215.5029263275</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>10594.2522405958</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11849.4582801006</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>14791.1381425738</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>17224.1995529681</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>18189.2630060511</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>19654.2368885291</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>23588.8416384073</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>27880.6481792873</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>26208.3513782914</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>25212.5890368519</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>26339.0103594949</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>23763.6610044249</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>23979.2453048522</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>24390.6403759545</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>730.654</t>
+          <t>11892.6881167295</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>746.326</t>
+          <t>12187.7699604307</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>753.734</t>
+          <t>13703.0084144848</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>839.508</t>
+          <t>17015.5229765542</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>985.667</t>
+          <t>19732.1613792298</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>1008.668</t>
+          <t>20753.0127773947</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>1025.488</t>
+          <t>22273.6204687774</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>1030.161</t>
+          <t>26672.3958402405</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1066.694</t>
+          <t>31473.735150386</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1066.353</t>
+          <t>29649.2101884721</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>969.128</t>
+          <t>28564.9214031948</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1003.47</t>
+          <t>30044.3488326818</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>953.598</t>
+          <t>27091.3360373735</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>934.724</t>
+          <t>27589.3601502296</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>837.208</t>
+          <t>28102.5630742369</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>62.76</t>
+          <t>70077.6380364196</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>59.79</t>
+          <t>69641.7752295007</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>74872.7648766688</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>49.69</t>
+          <t>93050.1990637697</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>110192.883584786</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>24.05</t>
+          <t>118564.843403705</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>22.43</t>
+          <t>126865.445390535</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>25.38</t>
+          <t>150212.437460841</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>25.39</t>
+          <t>173680.254313919</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>23.14</t>
+          <t>167577.66961286</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>33.15</t>
+          <t>163108.410917758</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>24.85</t>
+          <t>175885.573885247</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>164311.630729851</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>27.77</t>
+          <t>171418.39878552</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>172050.330956768</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.712</t>
+          <t>17779.2222017248</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.695</t>
+          <t>18414.9217841972</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.485</t>
+          <t>19081.8863897002</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>19154.0925733407</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>19991.0317408774</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.766</t>
+          <t>20498.5872847475</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.641</t>
+          <t>21434.7981017747</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>22553.9616503882</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.211</t>
+          <t>23540.739778423</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>22787.0691947345</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>23306.9198891347</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.274</t>
+          <t>22969.9439719061</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.341</t>
+          <t>22484.9712342143</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>22132.7825432119</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>22383.4466980504</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>15475.5693919639</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>16086.8858006541</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16611.1213354068</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>16794.6496118385</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>17495.3374727564</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18093.6559755527</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>18962.1994610957</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>19964.838752641</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>20795.6451712535</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>20124.0180076694</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>20571.7220324289</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>20194.1572938366</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>19759.4812491932</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>19288.8600930574</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>19502.9676038187</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5796.56034757517</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>6080.94955672874</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6994.2457478696</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>9036.29439069095</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>10544.1115720169</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>11206.7867094116</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>12555.7749273609</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>15550.6139100693</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>17400.0753872253</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>14480.5732235433</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>13304.7102736211</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>14646.2287673182</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>13027.4993838543</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>13544.4335207704</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>14716.6437531252</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1189232000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1192581000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1248047000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>1256695000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1284726000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>1251254000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>1255526000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1291599000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1337518000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1313150000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1290350000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1252858000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1214124000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1194287000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1212155000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1460318926.67031</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1452745165.57945</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1520946700.18349</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1524643555.18188</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1554983028.24434</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1512181466.57251</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1515366288.85154</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1554455877.69895</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1608306156.30953</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1594985639.75174</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1578753822.09547</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1537495074.62847</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1494105322.78378</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1495011981.6391</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1528746046.16553</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>926890642.993233</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>910401924.908224</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>926482502.741757</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>915305770.486015</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>926121796.757386</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>903783791.794445</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>892806178.514439</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>907199853.997014</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>936862278.920497</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>901728605.568638</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>885547200.056221</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>855643604.65616</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>827913488.079578</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>827892490.524408</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>848993373.903613</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>905570</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>916260</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>937430</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>931720</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>934020</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>928730</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>944280</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>975770</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1000820</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>982920</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>962070</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>945990</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>937600</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>926990</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>940150</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>740270</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>753080</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>769150</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>767820</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>771750</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>769370</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>782610</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>810710</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>832850</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>810640</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>788680</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>772690</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>762720</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>740590</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>744870</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1460318926.67031</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1452745165.57945</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1520946700.18349</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1524643555.18188</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1554983028.24434</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1512181466.57251</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1515366288.85154</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1554455877.69895</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1608306156.30953</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1594985639.75174</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1578753822.09547</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1537495074.62847</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1494105322.78378</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1495011981.6391</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1528746046.16553</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>1189232000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1192581000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1248047000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1256695000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>1284726000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>1251254000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1255526000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>1291599000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1337518000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1313150000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1290350000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1252858000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1214124000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1194287000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1212155000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>38579.1617399267</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>39325.6364436374</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>44418.3104480493</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>55448.700313368</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>65225.4463534792</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>69632.8395131956</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>77659.5813408991</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>96517.9437891536</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>111674.278972107</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>95346.169903852</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>93316.8537318963</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>99911.7744</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>89210.6965287903</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>91214.97048</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>94237.6435321417</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>17689.4540199267</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18269.0057236374</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>20697.2725280493</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>26051.527193368</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30276.0856134792</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>31960.2474131956</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>34829.4330608991</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>42223.2564391536</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>48874.2076521073</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>44129.392863852</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>41869.3532718963</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>44690.5776</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>40118.7454887903</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>41133.78039</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>42819.1138321417</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>106988.216988321</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>106056.298808335</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>104829.706236804</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>107529.971624431</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>113048.58345144</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>117857.371360434</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>121728.710600549</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>127642.792843801</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>131195.119678492</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>129051.167638648</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>133085.466459743</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>135172.092288674</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>138953.754534076</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>141796.945008355</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>143530.846312705</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Zero depreciation</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>zdW16</t>
